--- a/docs/图谱指标梳理-亿级科技知识图谱引擎-v1.xlsx
+++ b/docs/图谱指标梳理-亿级科技知识图谱引擎-v1.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Milvus 向量库（实体索引 collection，按图空间同名库）</t>
+          <t>Milvus 向量库（全局单一 kg_entity collection，graph_space 字段按图空间分区，主键 document_id=graph_space::vid）+ MySQL 控制库 kg_entity_search_state（每空间一行状态快照）</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>已索引实体数 = Milvus 实体索引 collection 当前向量条数；更新时间 = 最近一次重建完成时间</t>
+          <t>已索引实体数 = 控制库状态快照 entity_count（重建完成时写入；读取时经 Milvus 本空间有行校验，快照失效显示 0 并标记 stateStale）；更新时间 = 最近一次重建完成时间（状态行 updated_at）</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>按图空间统计（同名 Milvus 库）；浏览模式（图直查）不依赖索引。</t>
+          <t>按图空间统计（同一集合内按 graph_space 字段过滤，非按空间同名建库）；向量维度为集合级属性，切换 embedding 配置致维度变化时集合整体重建、其它图空间需各自重建；浏览模式（图直查）不依赖索引。</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>按图空间统计；属性为硬删除，删除即出统计。</t>
+          <t>实体/关系/核心/事实/推理类型计数按图空间过滤；属性字段/必填属性/约束/来源映射计数当前为全库口径（不随图空间过滤，见 dao/schema_management.py stats）；属性与 Schema 均为硬删除（物理删行+图库 DROP 列），删除即出统计。</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Schema 管理（统计）/ 图谱构建（可抽取 Schema 下拉）</t>
+          <t>Schema 管理（脚本/来源绑定状态）/ 图谱构建（建任务 Schema 选择，提交时逐个校验）</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>脚本覆盖率 =（有脚本且绑定≥1 来源表的未删除 Schema 数）÷（未删除 Schema 总数）× 100%</t>
+          <t>可抽取 = 已传脚本 + 绑定≥1 来源表 + 对象存储存在脚本本体（available=true）；覆盖率 =（可抽取的未删除 Schema 数）÷（未删除 Schema 总数）× 100%（推导值，页面无直接百分比展示）</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>按图空间过滤（可切全部空间）；以最近一次执行状态为准。</t>
+          <t>按图空间过滤（可切全部空间）；以最近一次执行状态为准；已暂停（任务级开关）优先于运行中判定，无执行记录/QUEUED 归「未运行」（汇总卡不展示该档）；四态分类由前端统一推导（deriveJobUnifiedStatus）。</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>决定入库路径：≥0.85 自动入库；&lt;0.85 生成 T_DIRECT 人工审核 case。</t>
+          <t>平台不设置信度数值门限：正常链路写前消歧得分 ≥0.85 且分差足够自动并入（阈值口径见 IDX-KG-024）；脚本标记 pendingReview 的低置信/歧义候选进人工审核——挂实体候选走 T_LINK 强制人工裁决（挂起实体的边端点悬在未决 vid 上，不再自动并入；不再新增 T_DIRECT，T_DIRECT 仅 kg.custom 声明式步存量）。注：审核页「低于自动入库阈值 0.85」为前端静态文案，与实现不符，建议修正。</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>按候选单体；页面展示保留两位小数，未设置显示“—”。</t>
+          <t>按候选单体；消歧候选得分为服务端 3 位小数（round(score,3)）；T_DIRECT 抽取置信度按原值展示，未设置显示「—」。</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
